--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487779_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487779_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0806</v>
+        <v>3.0974</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7213</v>
+        <v>4.6794</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.6407</v>
+        <v>-1.582</v>
       </c>
       <c r="G2" t="n">
         <v>-2.5238</v>
@@ -610,13 +610,13 @@
         <v>1.6649</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7907</v>
+        <v>0.8075</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0718</v>
+        <v>-0.1138</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8625</v>
+        <v>0.9212</v>
       </c>
       <c r="V2" t="n">
         <v>3.1488</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3967</v>
+        <v>2.1992</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1623</v>
+        <v>2.9061</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-0.7069</v>
       </c>
       <c r="G3" t="n">
         <v>-0.0545</v>
@@ -688,13 +688,13 @@
         <v>1.4568</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8435</v>
+        <v>0.646</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1239</v>
+        <v>-0.1323</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7197</v>
+        <v>0.7784</v>
       </c>
       <c r="V3" t="n">
         <v>3.2726</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.994</v>
+        <v>1.2186</v>
       </c>
       <c r="E4" t="n">
-        <v>2.209</v>
+        <v>2.3161</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.215</v>
+        <v>-1.0976</v>
       </c>
       <c r="G4" t="n">
         <v>0.1464</v>
@@ -766,13 +766,13 @@
         <v>0.4162</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4032</v>
+        <v>-0.1786</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5219</v>
+        <v>-0.4148</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1188</v>
+        <v>0.2362</v>
       </c>
       <c r="V4" t="n">
         <v>1.8751</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. AREVALO SAENZ</t>
+          <t>A. BIRD-JELINEK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5224</v>
+        <v>-0.1654</v>
       </c>
       <c r="E5" t="n">
-        <v>2.8156</v>
+        <v>0.758</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.2932</v>
+        <v>-0.9234</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.9151</v>
+        <v>-1.6145</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.546</v>
+        <v>-0.4136</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.3691</v>
+        <v>-1.201</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2615</v>
+        <v>0.598</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2435</v>
+        <v>0.0192</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.018</v>
+        <v>0.5788</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.6536</v>
+        <v>-2.2126</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3025</v>
+        <v>-0.4328</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.3512</v>
+        <v>-1.7798</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6244</v>
+        <v>0.8325</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6649</v>
+        <v>0.8325</v>
       </c>
       <c r="S5" t="n">
-        <v>2.8131</v>
+        <v>0.3867</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5526</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>1.2605</v>
+        <v>0.4567</v>
       </c>
       <c r="V5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="X5" t="n">
         <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.565</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-2.565</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. BIRD-JELINEK</t>
+          <t>Í. IBAÑEZ SERRANO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4347</v>
+        <v>-0.4955</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3713</v>
+        <v>0.0803</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.806</v>
+        <v>-0.5758</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.6145</v>
+        <v>0.3241</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4136</v>
+        <v>0.0384</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.201</v>
+        <v>0.2857</v>
       </c>
       <c r="J6" t="n">
-        <v>0.598</v>
+        <v>0.0384</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0192</v>
+        <v>0.0384</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5788</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.2126</v>
+        <v>0.2857</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4328</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.7798</v>
+        <v>0.2857</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8325</v>
+        <v>0.2081</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8325</v>
+        <v>0.2081</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1174</v>
+        <v>0.1398</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4567</v>
+        <v>0.0419</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5741000000000001</v>
+        <v>0.0979</v>
       </c>
       <c r="V6" t="n">
-        <v>0.23</v>
+        <v>-1.1675</v>
       </c>
       <c r="W6" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Í. IBAÑEZ SERRANO</t>
+          <t>B. AREVALO SAENZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6614</v>
+        <v>-0.914</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0269</v>
+        <v>1.7021</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6345</v>
+        <v>-2.6161</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3241</v>
+        <v>-2.9151</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0384</v>
+        <v>-1.546</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2857</v>
+        <v>-1.3691</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0384</v>
+        <v>-0.2615</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0384</v>
+        <v>-0.2435</v>
       </c>
       <c r="L7" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-2.6536</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-1.3025</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-1.3512</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.6244</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-1.0406</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.6649</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.3767</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.4392</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.9376</v>
+      </c>
+      <c r="V7" t="n">
         <v>0</v>
       </c>
-      <c r="M7" t="n">
-        <v>0.2857</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.2857</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.2081</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.2081</v>
-      </c>
-      <c r="S7" t="n">
-        <v>-0.0261</v>
-      </c>
-      <c r="T7" t="n">
-        <v>-0.06519999999999999</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.0391</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-1.1675</v>
-      </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.565</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1675</v>
+        <v>-2.565</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W. NIANG</t>
+          <t>S. SERRATO BALLETBO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5631</v>
+        <v>-1.2147</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2912</v>
+        <v>-0.0902</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2719</v>
+        <v>-1.1245</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0184</v>
+        <v>-1.1827</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7784</v>
+        <v>-0.8186</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.24</v>
+        <v>-0.3641</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1655</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0871</v>
+        <v>0.0959</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0784</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1839</v>
+        <v>-1.2697</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8655</v>
+        <v>-0.9145</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3184</v>
+        <v>-0.3551</v>
       </c>
       <c r="P8" t="n">
         <v>0.4162</v>
@@ -1078,28 +1078,28 @@
         <v>0.4162</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3771</v>
+        <v>-0.2182</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4567</v>
+        <v>-0.1771</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0796</v>
+        <v>-0.0411</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5838</v>
+        <v>-0.23</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5838</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. SERRATO BALLETBO</t>
+          <t>W. NIANG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,40 +1111,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5758</v>
+        <v>-1.3972</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3045</v>
+        <v>-0.184</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2713</v>
+        <v>-1.2131</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1827</v>
+        <v>-1.0184</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8186</v>
+        <v>-0.7784</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3641</v>
+        <v>-0.24</v>
       </c>
       <c r="J9" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.1655</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0959</v>
+        <v>0.0871</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.0784</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2697</v>
+        <v>-1.1839</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9145</v>
+        <v>-0.8655</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3551</v>
+        <v>-0.3184</v>
       </c>
       <c r="P9" t="n">
         <v>0.4162</v>
@@ -1156,22 +1156,22 @@
         <v>0.4162</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5793</v>
+        <v>-0.2112</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3915</v>
+        <v>-0.3495</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1879</v>
+        <v>0.1383</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.23</v>
+        <v>-0.5838</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.23</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0987</v>
+        <v>-1.8741</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4624</v>
+        <v>-1.3553</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6363</v>
+        <v>-0.5188</v>
       </c>
       <c r="G10" t="n">
         <v>-0.1734</v>
@@ -1234,13 +1234,13 @@
         <v>0.4162</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2603</v>
+        <v>-0.0357</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1957</v>
+        <v>-0.0886</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0646</v>
+        <v>0.0529</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L. OBAJO BELTRAN</t>
+          <t>P. SALL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.2137</v>
+        <v>-4.9633</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.595</v>
+        <v>-3.6696</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.6187</v>
+        <v>-1.2937</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.9379</v>
+        <v>-4.1953</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8912</v>
+        <v>-2.9617</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.0466</v>
+        <v>-1.2336</v>
       </c>
       <c r="J11" t="n">
-        <v>1.7813</v>
+        <v>-0.9008</v>
       </c>
       <c r="K11" t="n">
-        <v>1.0849</v>
+        <v>-1.8021</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6964</v>
+        <v>0.9013</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.7192</v>
+        <v>-3.2945</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.9761</v>
+        <v>-1.1596</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.7431</v>
+        <v>-2.1349</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.8325</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q11" t="n">
         <v>-2.0812</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2487</v>
+        <v>1.6649</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1084</v>
+        <v>0.9396</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0586</v>
+        <v>-0.21</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.167</v>
+        <v>1.1496</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.3351</v>
+        <v>-1.2914</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.3538</v>
+        <v>-0.4776</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.9813</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. SALL</t>
+          <t>L. OBAJO BELTRAN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.4058</v>
+        <v>-5.1242</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.6993</v>
+        <v>-0.9165</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7065</v>
+        <v>-4.2077</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.1953</v>
+        <v>-1.9379</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.9617</v>
+        <v>-0.8912</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.2336</v>
+        <v>-1.0466</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.9008</v>
+        <v>1.7813</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.8021</v>
+        <v>1.0849</v>
       </c>
       <c r="L12" t="n">
-        <v>0.9013</v>
+        <v>0.6964</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.2945</v>
+        <v>-3.7192</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1596</v>
+        <v>-1.9761</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.1349</v>
+        <v>-1.7431</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.4162</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q12" t="n">
         <v>-2.0812</v>
       </c>
       <c r="R12" t="n">
-        <v>1.6649</v>
+        <v>1.2487</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4972</v>
+        <v>-0.0188</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2396</v>
+        <v>-0.2628</v>
       </c>
       <c r="U12" t="n">
-        <v>1.7368</v>
+        <v>0.244</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2914</v>
+        <v>-2.3351</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.4776</v>
+        <v>-0.3538</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.8137</v>
+        <v>-1.9813</v>
       </c>
     </row>
     <row r="13">
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.9595</v>
+        <v>-9.6332</v>
       </c>
       <c r="E13" t="n">
-        <v>5.900199999999999</v>
+        <v>6.2264</v>
       </c>
       <c r="F13" t="n">
-        <v>-15.8597</v>
+        <v>-15.8596</v>
       </c>
       <c r="G13" t="n">
         <v>-15.1451</v>
       </c>
       <c r="H13" t="n">
-        <v>-9.797599999999999</v>
+        <v>-9.797600000000001</v>
       </c>
       <c r="I13" t="n">
         <v>-5.3475</v>
@@ -1444,10 +1444,10 @@
         <v>10.1659</v>
       </c>
       <c r="K13" t="n">
-        <v>1.287299999999999</v>
+        <v>1.2873</v>
       </c>
       <c r="L13" t="n">
-        <v>8.878299999999999</v>
+        <v>8.878300000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-25.3112</v>
@@ -1468,19 +1468,19 @@
         <v>10.4056</v>
       </c>
       <c r="S13" t="n">
-        <v>3.3075</v>
+        <v>3.6338</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.664</v>
+        <v>-1.3378</v>
       </c>
       <c r="U13" t="n">
-        <v>4.9716</v>
+        <v>4.9717</v>
       </c>
       <c r="V13" t="n">
-        <v>2.918699999999999</v>
+        <v>2.9187</v>
       </c>
       <c r="W13" t="n">
-        <v>8.844900000000001</v>
+        <v>8.844899999999999</v>
       </c>
       <c r="X13" t="n">
         <v>-5.9261</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.6281</v>
+        <v>7.6075</v>
       </c>
       <c r="E14" t="n">
-        <v>8.102</v>
+        <v>8.3163</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4739</v>
+        <v>-0.7088</v>
       </c>
       <c r="G14" t="n">
         <v>9.545</v>
@@ -1546,13 +1546,13 @@
         <v>1.6649</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2506</v>
+        <v>0.23</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8358</v>
+        <v>-0.6215000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0863</v>
+        <v>0.8515</v>
       </c>
       <c r="V14" t="n">
         <v>-1.7513</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.5636</v>
+        <v>3.5548</v>
       </c>
       <c r="E15" t="n">
-        <v>3.19</v>
+        <v>2.9757</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3736</v>
+        <v>0.5790999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>3.5231</v>
@@ -1624,13 +1624,13 @@
         <v>1.6649</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7483</v>
+        <v>-0.7571</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.46</v>
+        <v>-0.6743</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2883</v>
+        <v>-0.0828</v>
       </c>
       <c r="V15" t="n">
         <v>-0.4599</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.0633</v>
+        <v>2.9649</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9054</v>
+        <v>3.0125</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1579</v>
+        <v>-0.0476</v>
       </c>
       <c r="G16" t="n">
         <v>4.8336</v>
@@ -1702,13 +1702,13 @@
         <v>0.4162</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0216</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7177</v>
+        <v>-0.6105</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7392</v>
+        <v>0.5337</v>
       </c>
       <c r="V16" t="n">
         <v>-1.1675</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.2143</v>
+        <v>2.1057</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7968</v>
+        <v>2.0111</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4175</v>
+        <v>0.0946</v>
       </c>
       <c r="G17" t="n">
         <v>-2.8745</v>
@@ -1780,13 +1780,13 @@
         <v>1.8731</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2244</v>
+        <v>-0.333</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7053</v>
+        <v>-0.491</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4809</v>
+        <v>0.1579</v>
       </c>
       <c r="V17" t="n">
         <v>3.8564</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3059</v>
+        <v>1.6567</v>
       </c>
       <c r="E18" t="n">
-        <v>4.169</v>
+        <v>4.4905</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.8631</v>
+        <v>-2.8337</v>
       </c>
       <c r="G18" t="n">
         <v>4.3048</v>
@@ -1858,13 +1858,13 @@
         <v>1.8731</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8501</v>
+        <v>-0.4992</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7705</v>
+        <v>-0.4491</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0795</v>
+        <v>-0.0502</v>
       </c>
       <c r="V18" t="n">
         <v>-2.565</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9215</v>
+        <v>-0.7262</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6867</v>
+        <v>0.7938</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6081</v>
+        <v>-1.5201</v>
       </c>
       <c r="G19" t="n">
         <v>-1.1544</v>
@@ -1936,13 +1936,13 @@
         <v>1.2487</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0595</v>
+        <v>-0.8643</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8358</v>
+        <v>-0.7286</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2237</v>
+        <v>-0.1357</v>
       </c>
       <c r="V19" t="n">
         <v>0.4599</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. CORREIA</t>
+          <t>V. ORLOV STURMAN MAURIN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.242</v>
+        <v>-1.9553</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.9097</v>
+        <v>-0.5780999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6677</v>
+        <v>-1.3772</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2551</v>
+        <v>-1.0627</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5204</v>
+        <v>-0.5712</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2653</v>
+        <v>-0.4915</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2919</v>
+        <v>0.9337</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0959</v>
+        <v>0.1107</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1959</v>
+        <v>0.823</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0368</v>
+        <v>-1.9964</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4245</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4613</v>
+        <v>-1.3144</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.8325</v>
+        <v>-1.4568</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.4974</v>
+        <v>-2.0812</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6649</v>
+        <v>0.6244</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9806</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7111</v>
+        <v>-0.5981</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2695</v>
+        <v>-0.0052</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.6452</v>
+        <v>1.1675</v>
       </c>
       <c r="W20" t="n">
-        <v>-1.4152</v>
+        <v>1.1675</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V. ORLOV STURMAN MAURIN</t>
+          <t>S. CORREIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.268</v>
+        <v>-2.1286</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6853</v>
+        <v>-3.7669</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5827</v>
+        <v>1.6383</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.0627</v>
+        <v>0.2551</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5712</v>
+        <v>0.5204</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4915</v>
+        <v>-0.2653</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9337</v>
+        <v>0.2919</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1107</v>
+        <v>0.0959</v>
       </c>
       <c r="L21" t="n">
-        <v>0.823</v>
+        <v>0.1959</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.9964</v>
+        <v>-0.0368</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6820000000000001</v>
+        <v>0.4245</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.3144</v>
+        <v>-0.4613</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.4568</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.0812</v>
+        <v>-2.4974</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6244</v>
+        <v>1.6649</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.916</v>
+        <v>0.0939</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7053</v>
+        <v>-0.1462</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2107</v>
+        <v>0.2401</v>
       </c>
       <c r="V21" t="n">
-        <v>1.1675</v>
+        <v>-1.6452</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1675</v>
+        <v>-1.4152</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3844</v>
+        <v>-3.1201</v>
       </c>
       <c r="E22" t="n">
         <v>-1.3953</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.989</v>
+        <v>-1.7248</v>
       </c>
       <c r="G22" t="n">
         <v>-2.2249</v>
@@ -2170,13 +2170,13 @@
         <v>0.4162</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.762</v>
+        <v>-0.4978</v>
       </c>
       <c r="T22" t="n">
         <v>-0.6524</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1096</v>
+        <v>0.1546</v>
       </c>
       <c r="V22" t="n">
         <v>-0.8137</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>9.959300000000002</v>
+        <v>9.959400000000002</v>
       </c>
       <c r="E23" t="n">
         <v>15.8596</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.900100000000001</v>
+        <v>-5.9002</v>
       </c>
       <c r="G23" t="n">
         <v>15.1451</v>
@@ -2248,13 +2248,13 @@
         <v>11.4464</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.3075</v>
+        <v>-3.3076</v>
       </c>
       <c r="T23" t="n">
         <v>-4.9717</v>
       </c>
       <c r="U23" t="n">
-        <v>1.6641</v>
+        <v>1.6639</v>
       </c>
       <c r="V23" t="n">
         <v>-2.9188</v>
